--- a/TwelveLabors.xlsx
+++ b/TwelveLabors.xlsx
@@ -1,36 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="characters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="relics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_events" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labours" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_01" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_02" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_03" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_04" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_05" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_06" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_07" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_08" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_09" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_10" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_11" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_12" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_beowulf_01" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_beowulf_02" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_beowulf_03" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_kratos_01" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_kratos_02" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter_kratos_03" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="characters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="relics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="endings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="random_events" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="labours" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="chapter_01" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="chapter_02" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="chapter_03" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="chapter_04" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="chapter_05" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="chapter_06" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="chapter_07" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="chapter_08" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="chapter_09" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="chapter_10" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="chapter_11" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="chapter_12" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="chapter_13" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="chapter_beowulf_01" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="chapter_beowulf_02" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="chapter_beowulf_03" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="chapter_kratos_01" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="chapter_kratos_02" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="chapter_kratos_03" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1258,7 +1259,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch04_aftermath</t>
+          <t>ch04_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1268,22 +1269,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>山中老人</t>
+          <t>雪中幻象</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>你将野猪扛回城中。途中，一个老人出现在路边——他是酒神狄俄尼索斯的挚友。“年轻人，”他说，“真正的野兽不在山林，而在人心。”</t>
+          <t>扛着野猪下山，暴风雪骤然加剧。在白茫茫的雪幕中，你看见自己的倒影——但那不是你。倒影中的你双眼血红，嘴角挂着嗜血的笑。“杀戮让你快乐，不是吗？”它说。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>感谢老人，继续前行</t>
+          <t>承认内心的嗜血本性</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"智慧": 1, "疯狂": -1}</t>
+          <t>{"疯狂": 2, "力量": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -1292,36 +1293,50 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>embrace</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"bloodlust_accepted": true}</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>询问关于内心野兽的含义</t>
+          <t>否认幻象，坚守理性</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
+          <t>{"神恩": 1, "疯狂": -1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>智慧</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>幻象的嘲笑刺入你的心智。</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
           <t>{"疯狂": 1}</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>{"met_old_man": true}</t>
-        </is>
-      </c>
+      <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -1331,6 +1346,83 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch04_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>山中老人</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>你将野猪扛回城中。途中，一个老人出现在路边——他是酒神狄俄尼索斯的挚友。“年轻人，”他说，“真正的野兽不在山林，而在人心。”</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>感谢老人，继续前行</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"智慧": 1, "疯狂": -1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>询问关于内心野兽的含义</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>{"met_old_man": true}</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1343,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1878,7 +1970,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch05_aftermath</t>
+          <t>ch05_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1888,22 +1980,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>国王的承诺</t>
+          <t>污秽之语</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>一日之内，牛棚焕然一新。奥革阿斯王震惊了——但他拒绝支付报酬，声称你事先不知情。这是欺骗！你转身离开，心中种下怨恨的种子。</t>
+          <t>清理过半，污秽中传来低语。“加入我们……”腐败之声钻入耳膜。这些粪便并非寻常之物——它们是奥革阿斯王献祭给冥神的祭品腐烂而成。污秽正侵蚀你的神恩，每呼吸一口都在远离神明。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>记下这笔账，总有一天会清算</t>
+          <t>亵渎祭品，加速清理</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"疯狂": 1}</t>
+          <t>{"神恩": -2, "智慧": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -1912,28 +2004,46 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>desecrate</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"desecrated_offering": true}</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>放下怨恨，继续前行</t>
+          <t>净化祭品，再行清理</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"神恩": 1}</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
+          <t>{"神恩": 1, "生命": -1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>神恩</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>净化仪式失败，污秽反噬。</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1}</t>
+        </is>
+      </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>purify</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr"/>
@@ -1948,6 +2058,79 @@
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch05_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>国王的承诺</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>一日之内，牛棚焕然一新。奥革阿斯王震惊了——但他拒绝支付报酬，声称你事先不知情。这是欺骗！你转身离开，心中种下怨恨的种子。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>记下这笔账，总有一天会清算</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>放下怨恨，继续前行</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>{"神恩": 1}</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1959,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2494,7 +2677,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch06_aftermath</t>
+          <t>ch06_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2504,22 +2687,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>净化之地</t>
+          <t>智慧之盾</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>怪鸟或死或逃，湖泊恢复了平静。你用羽毛为自己制作了一顶头盔——青铜羽毛的保护。雅典娜在云端微笑，她认可了你的机智。</t>
+          <t>湖泊净化后，雅典娜的真身显现于云端。她抛下一面闪耀智慧之光的盾牌。“你证明了自己的机智，”她说，“此盾能看破一切幻象——但记住，智慧亦有代价。”</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>带着羽毛头盔继续前行</t>
+          <t>接受神盾，立誓效忠智慧</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"神恩": 1}</t>
+          <t>{"智慧": 1, "神恩": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -2528,20 +2711,44 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>athena_shield</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"pledged_to_athena": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>谢绝神盾，独行其道</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"荣耀": 2, "神恩": -1}</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>refuse</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"rejected_athena": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -2551,6 +2758,67 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch06_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>净化之地</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>怪鸟或死或逃，湖泊恢复了平静。你用羽毛为自己制作了一顶头盔——青铜羽毛的保护。雅典娜在云端微笑，她认可了你的机智。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>带着羽毛头盔继续前行</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"神恩": 1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2563,7 +2831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3098,7 +3366,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch07_aftermath</t>
+          <t>ch07_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3108,47 +3376,61 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>公主的告别</t>
+          <t>海神之怒</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>神牛终于安静下来。阿里阿德涅看着你，眼中满是钦佩。“你愿意带我离开克里特吗？”她低声问，“这迷宫困住了我太久。”</t>
+          <t>公牛被制服，大海却开始咆哮。波塞冬从浪涛中升起，三叉戟指向你。“你驯服了我的礼物，”他咆哮，“凡人不该触碰神之物！”巨浪如山般压来。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>答应带她离开</t>
+          <t>以力量抗衡海神之怒</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"疯狂": 1, "神恩": -1}</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>{"力量": 1, "生命": -1}</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>力量</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>海浪将你拍翻在礁石上。</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>{"生命": -2}</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>resist</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>{"ariadne_escaped": true}</t>
+          <t>{"poseidon_resisted": true}</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>拒绝，英雄不应被爱情羁绊</t>
+          <t>献祭公牛，平息海神</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 1}</t>
+          <t>{"神恩": 2, "荣耀": -1}</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -3157,11 +3439,15 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>sacrifice</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"bull_sacrificed": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -3171,6 +3457,83 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch07_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>公主的告别</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>神牛终于安静下来。阿里阿德涅看着你，眼中满是钦佩。“你愿意带我离开克里特吗？”她低声问，“这迷宫困住了我太久。”</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>答应带她离开</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1, "神恩": -1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>{"ariadne_escaped": true}</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>拒绝，英雄不应被爱情羁绊</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>{"荣耀": 1}</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3183,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3722,7 +4085,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch08_aftermath</t>
+          <t>ch08_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3732,22 +4095,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>暴君的终结</t>
+          <t>人性的重量</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>狄俄墨得斯死了——被他自己的马分食。你带着牝马群离开，从未回头。那些马现在温顺如羊，嗅不出曾经的嗜血本性。嗜血缰绳缠在你腰间，吸收了马群的野性。</t>
+          <t>你带着马群离开。但它们的眼神变了——不再是野兽的凶光，而是人的悲悯。它们吃过国王，如今用国王的眼睛看着你。“你和我们，有什么区别？”那眼神在问。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>带着战利品返回</t>
+          <t>驱散马群，独自前行</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2}</t>
+          <t>{"疯狂": 1, "荣耀": -1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -3756,20 +4119,40 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>release</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"mares_released": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>驯服马群，带它们回去</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"力量": 1, "神恩": -1}</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"mares_kept": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -3779,6 +4162,67 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch08_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>暴君的终结</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>狄俄墨得斯死了——被他自己的马分食。你带着牝马群离开，从未回头。那些马现在温顺如羊，嗅不出曾经的嗜血本性。嗜血缰绳缠在你腰间，吸收了马群的野性。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>带着战利品返回</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"荣耀": 2}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3791,7 +4235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4326,7 +4770,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch09_aftermath</t>
+          <t>ch09_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4336,22 +4780,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>战神的礼物</t>
+          <t>临终之言</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>无论你选择了哪条路，腰带现在在你手中。它散发着血腥的气息，诉说着一场又一场战争。赫拉在云端冷笑——她从不放过挑拨离间的机会。</t>
+          <t>希波吕忒倒在血泊中（或被你尊重地送别）。她抓住你的手腕，气若游丝。“腰带……不是战利品，”她低语，“它是诅咒。每个拥有它的男人，都会被战争吞噬。”她的眼睛渐渐失去光芒。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>带着战利品离开亚马逊</t>
+          <t>佩戴腰带，接受诅咒</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 1}</t>
+          <t>{"力量": 2, "疯狂": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -4360,20 +4804,54 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>wear</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"belt_worn": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>封存腰带，拒绝诅咒</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"神恩": 1, "荣耀": -1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>智慧</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>腰带的力量诱惑着你。</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"belt_sealed": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -4383,6 +4861,67 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch09_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>战神的礼物</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>无论你选择了哪条路，腰带现在在你手中。它散发着血腥的气息，诉说着一场又一场战争。赫拉在云端冷笑——她从不放过挑拨离间的机会。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>带着战利品离开亚马逊</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"荣耀": 1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4395,7 +4934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4930,7 +5469,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch10_aftermath</t>
+          <t>ch10_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4940,22 +5479,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>跨越大陆</t>
+          <t>冥界的影子</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>牛群跟着你穿越了整个欧洲大陆。一路上，赫拉克利特留下的食人巨牛不断骚扰。你赶走它们，继续前行——直到欧律斯修斯王的使者出现，宣告试炼结束。</t>
+          <t>跨越大陆途中，你路过一个深渊。深渊中传来三声犬吠——刻耳柏洛斯，你最终的宿命。一个蒙面人挡住去路：“去冥界之前，先回答我：你最害怕什么？”</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>将牛群交给国王</t>
+          <t>坦承恐惧：害怕变成怪物</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2}</t>
+          <t>{"疯狂": -1, "神恩": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -4964,20 +5503,40 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>truth</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"fear_admitted": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>拒绝回答，挥拳驱赶</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"力量": 1, "疯狂": 1}</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>refuse</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"fear_denied": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -4987,6 +5546,67 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch10_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>跨越大陆</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>牛群跟着你穿越了整个欧洲大陆。一路上，赫拉克利特留下的食人巨牛不断骚扰。你赶走它们，继续前行——直到欧律斯修斯王的使者出现，宣告试炼结束。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>将牛群交给国王</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"荣耀": 2}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4999,7 +5619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5534,7 +6154,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch11_aftermath</t>
+          <t>ch11_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5544,22 +6164,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>时间的诅咒</t>
+          <t>永恒的重量</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>金苹果在你手中，它们是永恒的象征。但从你触碰它们的那一刻起，某种不安的感觉开始蔓延——时间在你身上留下了痕迹。镜中的你似乎老了一些，又似乎从未改变。</t>
+          <t>金苹果在手中散发永恒的光芒。但每多看一秒，心智就被拉扯一分——时间在你周围扭曲，过去与未来同时涌来。时间诅咒已降临，每次抉择都会加深疯狂。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>带着苹果离开，不再回头</t>
+          <t>食用一颗金苹果，获得永恒</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"疯狂": 1}</t>
+          <t>{"生命": 3, "神恩": 2, "疯狂": 2}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -5568,24 +6188,58 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>eat</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>golden_apple</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>{"apples_obtained": true}</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+          <t>{"apple_eaten": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>不食禁果，仅带走</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1, "智慧": 1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>智慧</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>苹果的诱惑几乎压垮你的理智。</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 2}</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>resist</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"apple_resisted": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -5595,6 +6249,71 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch11_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>时间的诅咒</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>金苹果在你手中，它们是永恒的象征。但从你触碰它们的那一刻起，某种不安的感觉开始蔓延——时间在你身上留下了痕迹。镜中的你似乎老了一些，又似乎从未改变。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>带着苹果离开，不再回头</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>{"apples_obtained": true}</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5607,7 +6326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6172,7 +6891,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch12_aftermath</t>
+          <t>ch12_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6182,22 +6901,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>生死的边界</t>
+          <t>冥河之畔</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>你踏入了冥界，又活着走了出来。刻耳柏洛斯在你身后哀嚎——它从未被这样对待过。珀尔塞福涅在阴影中注视着你。“十二试炼已完成，”她低语，“但真正的考验才刚刚开始。”</t>
+          <t>刻耳柏洛斯安静下来后，你来到冥河畔。河水映出你的所有——活着的你，和已经死去的你。船夫卡戎撑着渡船靠近：“想看看自己死后的样子吗？免费的，英雄。”</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>带着冥界的印记返回人间</t>
+          <t>凝视冥河，直面死亡</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"神恩": 1}</t>
+          <t>{"疯狂": 1, "智慧": 2}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -6206,20 +6925,54 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>finish</t>
+          <t>gaze</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"stared_into_styx": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>拒绝卡戎，不回头</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"神恩": 1, "荣耀": 1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>神恩</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>冥河的水汽侵蚀了你的信念。</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>refuse</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"resisted_styx": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -6229,6 +6982,67 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch12_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>生死的边界</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>你踏入了冥界，又活着走了出来。刻耳柏洛斯在你身后哀嚎——它从未被这样对待过。珀尔塞福涅在阴影中注视着你。“十二试炼已完成，”她低语，“但真正的考验才刚刚开始。”</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>带着冥界的印记返回人间</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"神恩": 1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>finish</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6594,7 +7408,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>beowulf_ch01_arrival</t>
+          <t>ch13_arrival</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6604,22 +7418,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>格伦德尔的阴影</t>
+          <t>第十三试炼：被遗忘的回响</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>赫罗特大殿笼罩在恐惧之中。十二年来，巨魔格伦德尔每夜侵袭，将战士们从睡梦中拖走撕碎。你站在殿外，感受到大地的战栗——它在靠近。北风呼啸，荣耀将在今夜接受检验。</t>
+          <t>三场试炼已尽，你本该归来。但冥界之门在你身后并未合拢。一个没有面孔的身影从虚空中走出——它有着你的身形，你的呼吸，却没有你的名字。“我是你未曾走过的路，”它说，“第十三试炼，从未被记载。因为通过它的人，都选择了被遗忘。”</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>在殿中等待，徒手迎战格伦德尔</t>
+          <t>直面无面者，质问其身份</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2}</t>
+          <t>{"智慧": 1}</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -6628,19 +7442,19 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>bold</t>
+          <t>face</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>在黑暗中布置陷阱，以逸待劳</t>
+          <t>转身逃离，拒绝这场试炼</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>{"智慧": 1}</t>
+          <t>{"疯狂": 2}</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -6649,11 +7463,15 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>plan</t>
+          <t>flee</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>{"fled_thirteenth": true}</t>
+        </is>
+      </c>
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr"/>
       <c r="Y3" s="4" t="inlineStr"/>
@@ -6667,7 +7485,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>beowulf_ch01_combat</t>
+          <t>ch13_confrontation</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -6677,76 +7495,82 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>黑夜中的搏斗</t>
+          <t>命运的镜像</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>格伦德尔如夜魇般闯入殿中，它的爪子可以撕裂钢铁。但你没有逃跑——你抓住了那只魔爪，紧紧不放。巨魔惊恐地挣扎，却发现无法逃脱你的铁握。这一刻，人类的意志压倒了古老的黑暗。</t>
+          <t>无面者化作你的模样——但它比你更完整。它拥有你没有做出的选择，承担了你逃避的代价。“你害怕成为我，”它说，“但你也害怕不成为我。”它递来一顶荆棘编织的王冠，戴上它，便能看见一切真相——代价是永恒的疯狂。</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>徒手扯断格伦德尔的臂膀</t>
+          <t>戴上疯狂之冠，直视真相</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>{"荣耀": 4, "力量": 2, "生命": -2}</t>
+          <t>{"疯狂": 3, "智慧": 3}</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>格伦德尔的力量超乎想象，你被甩出，肋骨断裂。</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>{"生命": -3, "疯狂": 1}</t>
-        </is>
-      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
+          <t>crown</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>madness_crown</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>{"grendel_arm_torn": true}</t>
+          <t>{"wore_madness_crown": true}</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>利用殿柱的夹角固定住它，引兄弟们围攻</t>
+          <t>拒绝王冠，以凡人之躯抗衡</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>{"荣耀": 2, "智慧": 1, "神恩": 1}</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
+          <t>{"生命": -2, "荣耀": 3}</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>荣耀</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>战友们的阵型被格伦德尔打乱，你受到波及。</t>
+          <t>你的凡人之躯无法承受它的存在。</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -1}</t>
+          <t>{"疯狂": 2}</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>tactics</t>
+          <t>mortal</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>{"rejected_crown": true}</t>
+        </is>
+      </c>
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr"/>
@@ -6760,7 +7584,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>beowulf_ch01_aftermath</t>
+          <t>ch13_aftermath</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6770,22 +7594,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>赫罗特的黎明</t>
+          <t>被遗忘的终章</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>格伦德尔的臂膀高悬于赫罗特殿顶，血迹像一幅残酷的旗帜。赫罗斯加王的泪水流淌，他握住你的双手许久无言。宴席开始了，诗人唱起了你的名字。但你知道——格伦德尔的母亲，还在等待复仇。</t>
+          <t>无面者消散了——或者，它从未存在过。你独自站在虚空之中，身后是十二试炼的辉煌，前方是无尽的遗忘。你做出了选择，但没有人会记得。这，就是第十三试炼。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>享受荣耀，明日再战</t>
+          <t>接受被遗忘的命运</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2, "生命": 1}</t>
+          <t>{"神恩": 2}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -6794,19 +7618,23 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>feast</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"accepted_oblivion": true}</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>主动出击，追杀格伦德尔之母</t>
+          <t>拒绝遗忘，留下自己的印记</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 3, "生命": -1}</t>
+          <t>{"荣耀": 2, "疯狂": 1}</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -6815,15 +7643,15 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>pursue</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>golden_apple</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr"/>
+          <t>defy</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"defied_oblivion": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -6996,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -7484,7 +8312,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>beowulf_ch02_arrival</t>
+          <t>beowulf_ch01_arrival</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -7494,22 +8322,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>水下魔窟</t>
+          <t>格伦德尔的阴影</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>格伦德尔之母藏身于黑暗的水底魔窟。你跳入湖中，潜水半日才看到了她的巢穴。四周浸泡着战士的骨骸，墙上挂满锈蚀的武器。她比她的儿子更强大，更古老，更充满仇恨。</t>
+          <t>赫罗特大殿笼罩在恐惧之中。十二年来，巨魔格伦德尔每夜侵袭，将战士们从睡梦中拖走撕碎。你站在殿外，感受到大地的战栗——它在靠近。北风呼啸，荣耀将在今夜接受检验。</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>检视周围的武器，寻找可用之物</t>
+          <t>在殿中等待，徒手迎战格伦德尔</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>{"智慧": 1}</t>
+          <t>{"荣耀": 2}</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -7518,19 +8346,19 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>直接发起攻击，趁她不备</t>
+          <t>在黑暗中布置陷阱，以逸待劳</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 1, "疯狂": 1}</t>
+          <t>{"智慧": 1}</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -7539,7 +8367,7 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>charge</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr"/>
@@ -7557,7 +8385,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>beowulf_ch02_combat</t>
+          <t>beowulf_ch01_combat</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -7567,67 +8395,67 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>古剑的奇迹</t>
+          <t>黑夜中的搏斗</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>你的剑无法伤她分毫，她的爪子将你砸入地面。就在危急关头，你看见墙上挂着一把巨大的古剑——那是巨人时代的遗物，只有英雄才能举起。</t>
+          <t>格伦德尔如夜魇般闯入殿中，它的爪子可以撕裂钢铁。但你没有逃跑——你抓住了那只魔爪，紧紧不放。巨魔惊恐地挣扎，却发现无法逃脱你的铁握。这一刻，人类的意志压倒了古老的黑暗。</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>奋力举起古剑，斩向她的颈项</t>
+          <t>徒手扯断格伦德尔的臂膀</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>{"荣耀": 4, "力量": 1, "生命": -1}</t>
+          <t>{"荣耀": 4, "力量": 2, "生命": -2}</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>古剑太重，你无法举起，她扑向了你。</t>
+          <t>格伦德尔的力量超乎想象，你被甩出，肋骨断裂。</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -2, "疯狂": 2}</t>
+          <t>{"生命": -3, "疯狂": 1}</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ancient_sword</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>{"grendel_mother_slain": true, "ancient_sword_used": true}</t>
+          <t>{"grendel_arm_torn": true}</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>引她追逐，用水流旋涡困住她</t>
+          <t>利用殿柱的夹角固定住它，引兄弟们围攻</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>{"智慧": 3, "疯狂": -1}</t>
+          <t>{"荣耀": 2, "智慧": 1, "神恩": 1}</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>旋涡的力量不足，她挣脱了。</t>
+          <t>战友们的阵型被格伦德尔打乱，你受到波及。</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -2}</t>
+          <t>{"生命": -1}</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -7650,7 +8478,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>beowulf_ch02_aftermath</t>
+          <t>beowulf_ch01_aftermath</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -7660,22 +8488,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>湖底的遗宝</t>
+          <t>赫罗特的黎明</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>击败格伦德尔之母后，水底的魔法消散了，湖水开始净化。你在巢穴深处发现了格伦德尔家族世代积累的宝藏——还有一面看起来极为特别的盾牌。</t>
+          <t>格伦德尔的臂膀高悬于赫罗特殿顶，血迹像一幅残酷的旗帜。赫罗斯加王的泪水流淌，他握住你的双手许久无言。宴席开始了，诗人唱起了你的名字。但你知道——格伦德尔的母亲，还在等待复仇。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>带走盾牌，作为战利品</t>
+          <t>享受荣耀，明日再战</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 1}</t>
+          <t>{"荣耀": 2, "生命": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -7684,23 +8512,19 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>take_shield</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>athena_shield</t>
-        </is>
-      </c>
+          <t>feast</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>留下财宝，只带走荣耀</t>
+          <t>主动出击，追杀格伦德尔之母</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2, "神恩": 2}</t>
+          <t>{"荣耀": 3, "生命": -1}</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -7709,10 +8533,14 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>honor</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr"/>
+          <t>pursue</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>golden_apple</t>
+        </is>
+      </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
@@ -8088,7 +8916,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>beowulf_ch03_arrival</t>
+          <t>beowulf_ch02_arrival</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -8098,22 +8926,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>最后的龙</t>
+          <t>水下魔窟</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>五十年了。你已是须发皆白的老王，但龙的吐息正在烧毁你的王国。年轻的战士们吓得面如土色，只有你——站起来，穿上了锈迹斑斑的盔甲。人生最后一战，没有退路，只有荣耀。</t>
+          <t>格伦德尔之母藏身于黑暗的水底魔窟。你跳入湖中，潜水半日才看到了她的巢穴。四周浸泡着战士的骨骸，墙上挂满锈蚀的武器。她比她的儿子更强大，更古老，更充满仇恨。</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>独自前往龙穴，不愿战士送死</t>
+          <t>检视周围的武器，寻找可用之物</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 3, "生命": -1}</t>
+          <t>{"智慧": 1}</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -8122,19 +8950,19 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>alone</t>
+          <t>search</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>带上最忠心的战士维格拉夫</t>
+          <t>直接发起攻击，趁她不备</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 1, "力量": 1}</t>
+          <t>{"荣耀": 1, "疯狂": 1}</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -8143,7 +8971,7 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>together</t>
+          <t>charge</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr"/>
@@ -8161,7 +8989,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>beowulf_ch03_combat</t>
+          <t>beowulf_ch02_combat</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -8171,62 +8999,62 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>老王与龙</t>
+          <t>古剑的奇迹</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>龙的火焰融化了你的盾牌，它的爪子将你按在岩石上。生命正在流逝，但你的手还能动——你抓住了龙的脖子，将匕首刺入它柔软的腹部。同归于尽，还是奇迹？</t>
+          <t>你的剑无法伤她分毫，她的爪子将你砸入地面。就在危急关头，你看见墙上挂着一把巨大的古剑——那是巨人时代的遗物，只有英雄才能举起。</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>拼尽最后力气，双双同归于尽</t>
+          <t>奋力举起古剑，斩向她的颈项</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>{"荣耀": 8, "生命": -4}</t>
+          <t>{"荣耀": 4, "力量": 1, "生命": -1}</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>你的力量已油尽灯枯，无法完成最后的刺击。</t>
+          <t>古剑太重，你无法举起，她扑向了你。</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -3, "疯狂": 1}</t>
+          <t>{"生命": -2, "疯狂": 2}</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>sacrifice</t>
+          <t>ancient_sword</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>{"dragon_slain": true, "beowulf_fell": true}</t>
+          <t>{"grendel_mother_slain": true, "ancient_sword_used": true}</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>等待维格拉夫的援助，共同完成击杀</t>
+          <t>引她追逐，用水流旋涡困住她</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>{"荣耀": 4, "生命": -2, "神恩": 2}</t>
+          <t>{"智慧": 3, "疯狂": -1}</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>维格拉夫来得太迟，你已经被龙焰灼伤。</t>
+          <t>旋涡的力量不足，她挣脱了。</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
@@ -8236,15 +9064,11 @@
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>tactics</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>{"dragon_slain": true}</t>
-        </is>
-      </c>
+      <c r="V4" s="5" t="inlineStr"/>
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr"/>
@@ -8258,7 +9082,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>beowulf_ch03_aftermath</t>
+          <t>beowulf_ch02_aftermath</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -8268,22 +9092,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>英雄的黄昏</t>
+          <t>湖底的遗宝</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>龙死了。战士们围在你身边，他们终于明白了荣耀是什么。维格拉夫握住你的手，你将黄金颈链交给他。"传下去，"你说，"不是财富——是勇气。"诗人将在遥远的地方唱起这一刻，直到最后一个人类消失于世间。</t>
+          <t>击败格伦德尔之母后，水底的魔法消散了，湖水开始净化。你在巢穴深处发现了格伦德尔家族世代积累的宝藏——还有一面看起来极为特别的盾牌。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>闭上眼睛，安然接受命运</t>
+          <t>带走盾牌，作为战利品</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 3, "神恩": 3}</t>
+          <t>{"荣耀": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -8292,19 +9116,23 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>peace</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>take_shield</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>athena_shield</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>挣扎着站起，向部众宣告继续战斗</t>
+          <t>留下财宝，只带走荣耀</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 5, "生命": -2, "疯狂": 1}</t>
+          <t>{"荣耀": 2, "神恩": 2}</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -8313,7 +9141,7 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>defiance</t>
+          <t>honor</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr"/>
@@ -8692,7 +9520,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>kratos_ch01_arrival</t>
+          <t>beowulf_ch03_arrival</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -8702,22 +9530,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>阿瑞斯的命令</t>
+          <t>最后的龙</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>你曾向战神阿瑞斯发誓效忠，以换取力量战胜敌人。那一天你赢了，但代价是你的家人死在你自己的混沌之刃下。愤怒、悲痛、仇恨——这一切燃烧着，将你驱使向奥林匹斯的台阶。</t>
+          <t>五十年了。你已是须发皆白的老王，但龙的吐息正在烧毁你的王国。年轻的战士们吓得面如土色，只有你——站起来，穿上了锈迹斑斑的盔甲。人生最后一战，没有退路，只有荣耀。</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>压抑愤怒，冷静分析战略</t>
+          <t>独自前往龙穴，不愿战士送死</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>{"智慧": 1, "疯狂": -1}</t>
+          <t>{"荣耀": 3, "生命": -1}</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -8726,19 +9554,19 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>alone</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>释放内心的怒火，踏上杀神之路</t>
+          <t>带上最忠心的战士维格拉夫</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>{"力量": 1, "疯狂": 1}</t>
+          <t>{"荣耀": 1, "力量": 1}</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -8747,7 +9575,7 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>rage</t>
+          <t>together</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr"/>
@@ -8765,7 +9593,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>kratos_ch01_combat</t>
+          <t>beowulf_ch03_combat</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -8775,76 +9603,80 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>斯巴达之怒</t>
+          <t>老王与龙</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>阿瑞斯派出了他最强大的战士群来阻止你。他们是你昔日的同袍——但他们现在是神的走狗。混沌之刃在你手中旋转，链条如蛇般缠绕，斯巴达的战吼震裂了神殿的柱子。</t>
+          <t>龙的火焰融化了你的盾牌，它的爪子将你按在岩石上。生命正在流逝，但你的手还能动——你抓住了龙的脖子，将匕首刺入它柔软的腹部。同归于尽，还是奇迹？</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>斯巴达方阵，以力碾压一切</t>
+          <t>拼尽最后力气，双双同归于尽</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>{"力量": 3, "疯狂": 2, "荣耀": 1}</t>
+          <t>{"荣耀": 8, "生命": -4}</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>数量的优势压制了你，你被围困其中。</t>
+          <t>你的力量已油尽灯枯，无法完成最后的刺击。</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -2, "疯狂": 1}</t>
+          <t>{"生命": -3, "疯狂": 1}</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>strength</t>
+          <t>sacrifice</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>{"spartan_rage_used": true}</t>
+          <t>{"dragon_slain": true, "beowulf_fell": true}</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>以混沌之刃的锁链绑住首领要挟</t>
+          <t>等待维格拉夫的援助，共同完成击杀</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>{"智慧": 2, "神恩": -1, "力量": 1}</t>
+          <t>{"荣耀": 4, "生命": -2, "神恩": 2}</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>首领挣脱了锁链，反击刺伤了你。</t>
+          <t>维格拉夫来得太迟，你已经被龙焰灼伤。</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -1, "疯狂": 1}</t>
+          <t>{"生命": -2}</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>chains</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>{"dragon_slain": true}</t>
+        </is>
+      </c>
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr"/>
@@ -8858,7 +9690,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>kratos_ch01_aftermath</t>
+          <t>beowulf_ch03_aftermath</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -8868,22 +9700,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>灰烬中的誓言</t>
+          <t>英雄的黄昏</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>战场归于寂静。你望着自己灰白色的皮肤——那是你家人血液的颜色，永远洗不去的标记。"斯巴达幽灵"——他们这样叫你，不知是赞美还是诅咒。你不在乎。你只在乎一件事：弑神。</t>
+          <t>龙死了。战士们围在你身边，他们终于明白了荣耀是什么。维格拉夫握住你的手，你将黄金颈链交给他。"传下去，"你说，"不是财富——是勇气。"诗人将在遥远的地方唱起这一刻，直到最后一个人类消失于世间。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>在心中默念亡者的名字，继续前行</t>
+          <t>闭上眼睛，安然接受命运</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"疯狂": -1, "荣耀": 1}</t>
+          <t>{"荣耀": 3, "神恩": 3}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -8892,19 +9724,19 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>grieve</t>
+          <t>peace</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>压制悲痛，怒火就是你的武器</t>
+          <t>挣扎着站起，向部众宣告继续战斗</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"疯狂": 2, "力量": 1}</t>
+          <t>{"荣耀": 5, "生命": -2, "疯狂": 1}</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -8913,7 +9745,7 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>defiance</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr"/>
@@ -9292,7 +10124,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>kratos_ch02_arrival</t>
+          <t>kratos_ch01_arrival</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -9302,22 +10134,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>海神的王座</t>
+          <t>阿瑞斯的命令</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>波塞冬骑着海浪兽从天而降，大地震颤。"你以为你能杀死神明？"他狂笑道，海水淹没了半个王国。他是第一位阻拦你的奥林匹斯神明。怒火在你的血液中燃烧——海神，今日便是你的末日。</t>
+          <t>你曾向战神阿瑞斯发誓效忠，以换取力量战胜敌人。那一天你赢了，但代价是你的家人死在你自己的混沌之刃下。愤怒、悲痛、仇恨——这一切燃烧着，将你驱使向奥林匹斯的台阶。</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>等待波塞冬靠近，寻找破绽</t>
+          <t>压抑愤怒，冷静分析战略</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>{"智慧": 1, "疯狂": 1}</t>
+          <t>{"智慧": 1, "疯狂": -1}</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -9326,19 +10158,19 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>cold</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>直接冲向他的海浪兽</t>
+          <t>释放内心的怒火，踏上杀神之路</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>{"力量": 1, "疯狂": 2}</t>
+          <t>{"力量": 1, "疯狂": 1}</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -9347,7 +10179,7 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>charge</t>
+          <t>rage</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr"/>
@@ -9365,7 +10197,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>kratos_ch02_combat</t>
+          <t>kratos_ch01_combat</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -9375,62 +10207,62 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>弑神的瞬间</t>
+          <t>斯巴达之怒</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>海浪兽倒下了，波塞冬跌落在岩石上，狼狈挣扎。他第一次感到恐惧——神明的眼睛里出现了凡人的情感。这就是你一直在寻找的东西：让诸神知道什么是恐惧。你的双手掐住他的喉咙。</t>
+          <t>阿瑞斯派出了他最强大的战士群来阻止你。他们是你昔日的同袍——但他们现在是神的走狗。混沌之刃在你手中旋转，链条如蛇般缠绕，斯巴达的战吼震裂了神殿的柱子。</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>亲手了结波塞冬，用双手</t>
+          <t>斯巴达方阵，以力碾压一切</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>{"力量": 2, "疯狂": 3, "神恩": -3}</t>
+          <t>{"力量": 3, "疯狂": 2, "荣耀": 1}</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>神明的余力超出预料，他挣脱了你的手。</t>
+          <t>数量的优势压制了你，你被围困其中。</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>{"生命": -2, "疯狂": 2}</t>
+          <t>{"生命": -2, "疯狂": 1}</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>bare_hands</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>{"poseidon_slain": true, "first_god_killed": true}</t>
+          <t>{"spartan_rage_used": true}</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>用混沌之刃刺穿他，快而干净</t>
+          <t>以混沌之刃的锁链绑住首领要挟</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>{"力量": 1, "疯狂": 2, "神恩": -2}</t>
+          <t>{"智慧": 2, "神恩": -1, "力量": 1}</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>混沌之刃被海水腐蚀，力量不足。</t>
+          <t>首领挣脱了锁链，反击刺伤了你。</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
@@ -9440,15 +10272,11 @@
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>blade</t>
+          <t>chains</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>{"poseidon_slain": true}</t>
-        </is>
-      </c>
+      <c r="V4" s="5" t="inlineStr"/>
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr"/>
@@ -9462,7 +10290,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>kratos_ch02_aftermath</t>
+          <t>kratos_ch01_aftermath</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -9472,22 +10300,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>诸神的战栗</t>
+          <t>灰烬中的誓言</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>波塞冬死了。奥林匹斯的神明们第一次真正感到了恐惧。宙斯在云端望着你，他的眼神既是愤怒，也是——你能读出来——恐惧？不，还有别的什么。但现在不重要。还有更多的神明要杀。</t>
+          <t>战场归于寂静。你望着自己灰白色的皮肤——那是你家人血液的颜色，永远洗不去的标记。"斯巴达幽灵"——他们这样叫你，不知是赞美还是诅咒。你不在乎。你只在乎一件事：弑神。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>收集波塞冬的神器</t>
+          <t>在心中默念亡者的名字，继续前行</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"神恩": -1, "力量": 2}</t>
+          <t>{"疯狂": -1, "荣耀": 1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -9496,23 +10324,19 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>loot</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>madness_crown</t>
-        </is>
-      </c>
+          <t>grieve</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>不需要战利品，继续前行</t>
+          <t>压制悲痛，怒火就是你的武器</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2, "疯狂": -1}</t>
+          <t>{"疯狂": 2, "力量": 1}</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -9521,7 +10345,7 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr"/>
@@ -9900,6 +10724,614 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>kratos_ch02_arrival</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>海神的王座</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>波塞冬骑着海浪兽从天而降，大地震颤。"你以为你能杀死神明？"他狂笑道，海水淹没了半个王国。他是第一位阻拦你的奥林匹斯神明。怒火在你的血液中燃烧——海神，今日便是你的末日。</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>等待波塞冬靠近，寻找破绽</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>{"智慧": 1, "疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>直接冲向他的海浪兽</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>{"力量": 1, "疯狂": 2}</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="inlineStr"/>
+      <c r="AE3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>kratos_ch02_combat</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>弑神的瞬间</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>海浪兽倒下了，波塞冬跌落在岩石上，狼狈挣扎。他第一次感到恐惧——神明的眼睛里出现了凡人的情感。这就是你一直在寻找的东西：让诸神知道什么是恐惧。你的双手掐住他的喉咙。</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>亲手了结波塞冬，用双手</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>{"力量": 2, "疯狂": 3, "神恩": -3}</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>神明的余力超出预料，他挣脱了你的手。</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>{"生命": -2, "疯狂": 2}</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>bare_hands</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>{"poseidon_slain": true, "first_god_killed": true}</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>用混沌之刃刺穿他，快而干净</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>{"力量": 1, "疯狂": 2, "神恩": -2}</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>混沌之刃被海水腐蚀，力量不足。</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>{"生命": -1, "疯狂": 1}</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>blade</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>{"poseidon_slain": true}</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr"/>
+      <c r="AC4" s="5" t="inlineStr"/>
+      <c r="AD4" s="5" t="inlineStr"/>
+      <c r="AE4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>kratos_ch02_aftermath</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>诸神的战栗</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>波塞冬死了。奥林匹斯的神明们第一次真正感到了恐惧。宙斯在云端望着你，他的眼神既是愤怒，也是——你能读出来——恐惧？不，还有别的什么。但现在不重要。还有更多的神明要杀。</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>收集波塞冬的神器</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>{"神恩": -1, "力量": 2}</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>loot</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>madness_crown</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>不需要战利品，继续前行</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"荣耀": 2, "疯狂": -1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr"/>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t># 事件ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t># 类型(story)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t># 标题</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t># 正文</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t># 选1文本</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t># 选1效果</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t># 选1检定属性</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t># 选1检定值</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t># 选1失败文本</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t># 选1失败效果</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t># 选1分支</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t># 选1遗物ID</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t># 选1世界状态JSON</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t># 选2文本</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t># 选2效果</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t># 选2检定属性</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t># 选2检定值</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t># 选2失败文本</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t># 选2失败效果</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t># 选2分支</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t># 选2遗物ID</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t># 选2世界状态JSON</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t># 选3文本</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t># 选3效果</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t># 选3检定属性</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t># 选3检定值</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t># 选3失败文本</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t># 选3失败效果</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t># 选3分支</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t># 选3遗物ID</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t># 选3世界状态JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>option1_text</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>option1_effects</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>option1_req_stat</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>option1_req_val</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>option1_fail_text</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>option1_fail_effects</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>option1_branch</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>option1_relic</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>option1_world_state</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>option2_text</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>option2_effects</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>option2_req_stat</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>option2_req_val</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>option2_fail_text</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>option2_fail_effects</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>option2_branch</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>option2_relic</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>option2_world_state</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>option3_text</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>option3_effects</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>option3_req_stat</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>option3_req_val</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>option3_fail_text</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>option3_fail_effects</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>option3_branch</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>option3_relic</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>option3_world_state</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>kratos_ch03_arrival</t>
         </is>
       </c>
@@ -10653,7 +12085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10709,44 +12141,44 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>ending_immortal</t>
+          <t>ending_abyss_return</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>升格半神</t>
+          <t>深渊归来</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>三度试炼圆满，你的名字被刻入星空。你成为不朽，但也永远失去了凡人的自由。</t>
+          <t>你以追随者的血肉喂食了地狱犬，从此冥界的气息再未离开你。你从深渊归来，却不再是人。你成了行走的死亡，连诸神都不敢直视你的眼睛。</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&gt;=", "value": 15}, {"type": "stat", "name": "神恩", "op": "&gt;=", "value": 10}, {"type": "counter", "name": "labors_completed", "op": "==", "value": 3}]}</t>
+          <t>{"logic": "AND", "rules": [{"type": "flag", "name": "fed_companions", "value": true}]}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ending_glory_death</t>
+          <t>ending_mad_king</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>荣耀之死</t>
+          <t>疯王</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>你力竭而亡，但吟游诗人将传唱你的名字，直到诸神黄昏。</t>
+          <t>疯狂彻底吞噬了你的王座。你在空旷的宫殿中自言自语，对着不存在的臣民发号施令。你是英雄，也是疯子——但没人分得清哪个才是真的。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&gt;=", "value": 12}, {"type": "stat", "name": "生命", "op": "&lt;=", "value": 2}]}</t>
+          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "疯狂", "op": "&gt;=", "value": 18}]}</t>
         </is>
       </c>
     </row>
@@ -10775,88 +12207,88 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ending_beastmaster</t>
+          <t>ending_beast</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>野兽之王</t>
+          <t>无名野兽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>三场纯粹的肉体试炼，你成了荒野的化身。鲜血与咆哮是你唯一的语言。</t>
+          <t>荣耀熄灭，疯狂燃烧。你不再记得自己的名字，只记得撕咬与咆哮。你成了传说中那头无名的野兽，在荒野中游荡，直到时间的尽头。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>{"logic": "AND", "rules": [{"type": "path_sequence", "value": ["physical", "physical", "physical"]}]}</t>
+          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "疯狂", "op": "&gt;=", "value": 15}, {"type": "stat", "name": "荣耀", "op": "&lt;=", "value": 5}]}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ending_sage</t>
+          <t>ending_nameless</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>智者</t>
+          <t>无名之辈</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>你用智慧征服所有考验，但世人畏惧你的城府。你注定孤独。</t>
+          <t>你的名字无人知晓。你完成了试炼，却没有人传唱。你消失在历史的尘埃里，仿佛从未存在过。</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>{"logic": "AND", "rules": [{"type": "path_sequence", "value": ["mental", "mental", "mental"]}]}</t>
+          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&lt;=", "value": 0}, {"type": "counter", "name": "labors_completed", "op": "&gt;=", "value": 3}]}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ending_ascended</t>
+          <t>ending_immortal</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>升神</t>
+          <t>升格半神</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>你直面神明，并取而代之。奥林匹斯的王座已易主。</t>
+          <t>三度试炼圆满，你的名字被刻入星空。你成为不朽，但也永远失去了凡人的自由。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>{"logic": "AND", "rules": [{"type": "path_sequence", "value": ["divine", "divine", "divine"]}]}</t>
+          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&gt;=", "value": 15}, {"type": "stat", "name": "神恩", "op": "&gt;=", "value": 10}, {"type": "counter", "name": "labors_completed", "op": "==", "value": 3}]}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ending_beowulf_legend</t>
+          <t>ending_glory_death</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>不朽传奇</t>
+          <t>荣耀之死</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>贝奥武夫的事迹被刻进北境的岩石，永世流传。英雄不死，英雄只是化成了传说。</t>
+          <t>你力竭而亡，但吟游诗人将传唱你的名字，直到诸神黄昏。</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&gt;=", "value": 20}, {"type": "counter", "name": "labors_completed", "op": "==", "value": 3}]}</t>
+          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&gt;=", "value": 12}, {"type": "stat", "name": "生命", "op": "&lt;=", "value": 2}]}</t>
         </is>
       </c>
     </row>
@@ -10885,20 +12317,108 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>ending_beowulf_legend</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>不朽传奇</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>贝奥武夫的事迹被刻进北境的岩石，永世流传。英雄不死，英雄只是化成了传说。</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>{"logic": "AND", "rules": [{"type": "stat", "name": "荣耀", "op": "&gt;=", "value": 20}, {"type": "counter", "name": "labors_completed", "op": "==", "value": 3}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ending_ascended</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>升神</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>你直面神明，并取而代之。奥林匹斯的王座已易主。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>{"logic": "AND", "rules": [{"type": "path_sequence", "value": ["divine", "divine", "divine"]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ending_beastmaster</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>野兽之王</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>三场纯粹的肉体试炼，你成了荒野的化身。鲜血与咆哮是你唯一的语言。</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>{"logic": "AND", "rules": [{"type": "path_sequence", "value": ["physical", "physical", "physical"]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ending_sage</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>智者</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>你用智慧征服所有考验，但世人畏惧你的城府。你注定孤独。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>{"logic": "AND", "rules": [{"type": "path_sequence", "value": ["mental", "mental", "mental"]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>ending_mad_god</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>疯神降临</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>你彻底失去理智，但获得了神明的力量。</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>{"logic":"AND","rules":[{"type":"stat","name":"疯狂","op":"&gt;=","value":15}]}</t>
         </is>
@@ -12111,7 +13631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12654,7 +14174,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch01_aftermath</t>
+          <t>ch01_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -12664,40 +14184,64 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>狮皮披身</t>
+          <t>狮皮的代价</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>狮子已死。它的皮毛——你剥下这不朽的铠甲，披在身上。刀枪不入的狮皮将成为你最坚实的护盾。</t>
+          <t>狮皮剥下，却沉甸甸压在肩上——巨狮的怨念未散。一个披着鸦羽斗篷的老妪从岩石后走出，目光如炬。“狮皮认主，”她嘶哑道，“要么用你的血喂它，要么让它的灵魂啃噬你的梦。”</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>继续前行，接受下一试炼</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>以鲜血激活狮皮的力量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>{"生命": -1, "力量": 1}</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>blood</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"lion_blood_pact": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>拒绝献祭，承受狮魂低语</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 2, "神恩": 1}</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>refuse</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"lion_soul_whisper": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -12707,6 +14251,63 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch01_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>狮皮披身</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>狮子已死。它的皮毛——你剥下这不朽的铠甲，披在身上。刀枪不入的狮皮将成为你最坚实的护盾。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>继续前行，接受下一试炼</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12719,7 +14320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13254,7 +14855,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch02_aftermath</t>
+          <t>ch02_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -13264,44 +14865,78 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>毒血之河</t>
+          <t>不朽之颅</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>九头蛇终于倒下，剧毒的血液渗入大地。你浑身是伤，但活了下来。你用毒蛇之血浸泡箭矢——从此你的箭带有剧毒。</t>
+          <t>九头蛇躯体倒下，但中央那颗最大的头颅——传说中的不朽之头——仍在蠕动，发出嘶嘶声。它无法被杀死，只能被埋葬。再生之力仍在延续，每一瞬都在啃噬你的生机。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>用毒血涂抹武器，继续前行</t>
+          <t>以巨石镇压，深埋不朽之头</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"神恩": -1}</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>{"力量": 1, "荣耀": 1}</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>力量</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>巨石太重，砸伤了你的腿。</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>{"生命": -1}</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>seal</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"hydra_immortal_sealed": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>以毒血腐蚀，使其永眠</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"疯狂": 2, "智慧": 1}</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"hydra_poisoned": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -13311,6 +14946,67 @@
       <c r="AC5" s="4" t="inlineStr"/>
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch02_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>毒血之河</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>九头蛇终于倒下，剧毒的血液渗入大地。你浑身是伤，但活了下来。你用毒蛇之血浸泡箭矢——从此你的箭带有剧毒。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>用毒血涂抹武器，继续前行</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"神恩": -1}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13323,7 +15019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13854,7 +15550,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ch03_aftermath</t>
+          <t>ch03_twist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -13864,22 +15560,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>女神的礼物</t>
+          <t>月神的审视</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>一年的追逐后，牝鹿终于停下脚步，用那双金色的眼睛看着你。你轻轻抚摸它的脖颈，它允许你骑在它背上。你将它带回了迈锡尼。</t>
+          <t>牝鹿被捕获，天空却骤然暗下。阿尔忒弥斯降临，银弓搭箭，瞄准你的心口。“凡人，”她的声音如寒冰，“你触碰了我的圣物。给我一个理由，不取你性命。”</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>将神鹿献给欧律斯修斯王</t>
+          <t>单膝跪地，恳求女神宽恕</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"荣耀": 2}</t>
+          <t>{"神恩": 2, "荣耀": -1}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -13888,20 +15584,54 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>continue</t>
+          <t>mercy</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>{"artemis_forgiven": true}</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>直视女神，陈述试炼之命</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>{"荣耀": 2, "神恩": -1}</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>荣耀</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>你的傲慢激怒了女神。</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>{"神恩": -2, "生命": -1}</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>defiance</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>{"artemis_defied": true}</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
@@ -13912,6 +15642,67 @@
       <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ch03_aftermath</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>女神的礼物</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>一年的追逐后，牝鹿终于停下脚步，用那双金色的眼睛看着你。你轻轻抚摸它的脖颈，它允许你骑在它背上。你将它带回了迈锡尼。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>将神鹿献给欧律斯修斯王</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>{"荣耀": 2}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
+      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AE6" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
